--- a/hira_material_automation/output/monthly/202601_202605__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__temporary_synovial_substitute__250099__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>8415</t>
@@ -519,7 +523,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>7784</t>
@@ -552,7 +560,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>7662</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:06:26</t>
+          <t>2026-05-14T22:14:40</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cf671d449615ca2ce42e023391d32dac4dcb190adb2997b862c442a9a0134fb7</t>
+          <t>1ed15b701aa0b6a5747ba11521ec00f16f2bb5cac5c77d5bcec79ab0a5d0973e</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__temporary_synovial_substitute__250099__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:14:40</t>
+          <t>2026-05-24T21:59:01</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1ed15b701aa0b6a5747ba11521ec00f16f2bb5cac5c77d5bcec79ab0a5d0973e</t>
+          <t>9b8971d1852bcb9a22424a9470a1caa7a9425732ae17505cf2bd461db39f9734</t>
         </is>
       </c>
     </row>
